--- a/data/2026-08-11-virtual-tdrx-review-training-v0.1.xlsx
+++ b/data/2026-08-11-virtual-tdrx-review-training-v0.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10092" tabRatio="488" activeTab="8"/>
+    <workbookView windowWidth="23040" windowHeight="10740" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="保密级别 Confidentiality" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="333">
   <si>
     <t>名称 TITLE</t>
   </si>
@@ -1139,13 +1139,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>评审依据（数据</t>
     </r>
     <r>
@@ -1242,12 +1235,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>线损范围如无法控制，会吃掉技术本身带来的性能提升，导致量产后价值</t>
     </r>
     <r>
@@ -1370,12 +1357,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>确认</t>
     </r>
     <r>
@@ -1399,13 +1380,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>06.28</t>
     </r>
     <r>
@@ -1463,196 +1437,22 @@
 新型TDT项目差异Q&amp;A</t>
   </si>
   <si>
-    <t>虚拟智能终端协同增强（TRAIN-001）</t>
-  </si>
-  <si>
     <t>TDR1</t>
   </si>
   <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>虚拟项目经理甲</t>
-  </si>
-  <si>
-    <t>技术路线可行，需补齐关键器件边界、功耗预算和首轮验证计划后并行推进。</t>
-  </si>
-  <si>
     <t>评审依据（数据&amp;标准&amp;测试或技术逻辑等）</t>
   </si>
   <si>
-    <t>关键器件能力边界需要用样片数据闭环，否则后续方案选型存在偏差。</t>
-  </si>
-  <si>
-    <t>链路预算对温漂和批次差异的余量不足，需要增加最差条件校核。</t>
-  </si>
-  <si>
     <t>PCB</t>
   </si>
   <si>
-    <t>部分参加</t>
-  </si>
-  <si>
     <t>硬件测试</t>
   </si>
   <si>
-    <t>验证计划缺少弱网和高温组合场景，无法覆盖核心技术风险。</t>
-  </si>
-  <si>
-    <t>质量门限应在TDR1阶段明确并与后续量产判定保持一致。</t>
-  </si>
-  <si>
     <t>创新项目</t>
   </si>
   <si>
-    <t>TDR1-1</t>
-  </si>
-  <si>
-    <t>高腾飞、滕帅、杨凯、刘振岩</t>
-  </si>
-  <si>
-    <t>关键器件边界、链路余量和组合场景验证尚未形成统一基线。</t>
-  </si>
-  <si>
-    <t>建立统一技术基线，补充最差条件链路预算及弱网高温组合验证计划。</t>
-  </si>
-  <si>
-    <t>评审基线文档完成会签；仿真余量不低于3 dB；组合场景用例覆盖率达到100%。</t>
-  </si>
-  <si>
-    <t>03.25：基线与验证计划已更新，等待首轮样片数据。</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>TDR1-2</t>
-  </si>
-  <si>
-    <t>整机天线布局需要提前预留隔离区，避免结构冻结后返工。</t>
-  </si>
-  <si>
-    <t>在结构草图中标记天线净空区并纳入设计检查表。</t>
-  </si>
-  <si>
-    <t>结构草图通过天线与结构联合评审，净空尺寸满足设计规范。</t>
-  </si>
-  <si>
-    <t>03.22：联合评审完成。</t>
-  </si>
-  <si>
     <t>TDR2</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>Redirect</t>
-  </si>
-  <si>
-    <t>样片结果暴露高温稳定性风险，完成根因定位和回归验证前不得进入设计冻结。</t>
-  </si>
-  <si>
-    <t>Go（逾期）</t>
-  </si>
-  <si>
-    <t>高温样片数据超过技术基线，尚不能证明方案达到冻结条件。</t>
-  </si>
-  <si>
-    <t>挂会</t>
-  </si>
-  <si>
-    <t>射频校准偏差集中在高温区间，需要增加分段补偿。</t>
-  </si>
-  <si>
-    <t>结构热路径与仿真假设不一致，需要重新核对边界条件。</t>
-  </si>
-  <si>
-    <t>吴贞奇</t>
-  </si>
-  <si>
-    <t>回归测试尚未覆盖高温连续运行和恢复场景。</t>
-  </si>
-  <si>
-    <t>Go with Risk（逾期）</t>
-  </si>
-  <si>
-    <t>关键风险已识别，但关闭证据提交晚于会签时限。</t>
-  </si>
-  <si>
-    <t>TDR2-1</t>
-  </si>
-  <si>
-    <t>高腾飞、滕帅、刘振岩</t>
-  </si>
-  <si>
-    <t>高温条件下链路性能下降，样片结果超出TDR1技术基线。</t>
-  </si>
-  <si>
-    <t>完成根因分层定位，增加高温分段校准并重新执行全链路回归。</t>
-  </si>
-  <si>
-    <t>连续高温运行8小时无异常，链路余量不低于3 dB，三轮回归结果一致。</t>
-  </si>
-  <si>
-    <t>06.08：校准方案已合入，第二轮回归通过。</t>
-  </si>
-  <si>
-    <t>TDR2-2</t>
-  </si>
-  <si>
-    <t>罗勇平、杨凯</t>
-  </si>
-  <si>
-    <t>结构热路径假设与实测不一致，高温连续运行场景覆盖不足。</t>
-  </si>
-  <si>
-    <t>重新标定热仿真边界，并增加高温连续运行与恢复测试。</t>
-  </si>
-  <si>
-    <t>06.05：边界条件已重算，测试通过条件待补充。</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>核心指标已达到目标，遗留的量产一致性和长期稳定性问题可按计划并行关闭。</t>
-  </si>
-  <si>
-    <t>量产校准参数尚未覆盖全部器件批次，需要补充抽样策略。</t>
-  </si>
-  <si>
-    <t>改派（部分）</t>
-  </si>
-  <si>
-    <t>量产一致性风险需要通过三批次试产数据确认。</t>
-  </si>
-  <si>
-    <t>长期稳定性测试已启动，但尚未达到完整周期。</t>
-  </si>
-  <si>
-    <t>赵阳、杨凯</t>
-  </si>
-  <si>
-    <t>量产一致性和长期稳定性证据尚未覆盖完整批次与周期。</t>
-  </si>
-  <si>
-    <t>完成三批次试产抽检，并持续执行500小时稳定性测试。</t>
-  </si>
-  <si>
-    <t>三批次关键指标通过率不低于99%；500小时测试无严重故障。</t>
-  </si>
-  <si>
-    <t>08.10：首批试产通过，稳定性测试累计180小时。</t>
-  </si>
-  <si>
-    <t>量产校准参数对器件批次差异的覆盖范围待确认。</t>
-  </si>
-  <si>
-    <t>补充跨批次抽样并更新校准参数边界。</t>
-  </si>
-  <si>
-    <t>08.09：已完成抽样方案，判定阈值待补充。</t>
   </si>
 </sst>
 </file>
@@ -1662,8 +1462,8 @@
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="58">
     <font>
@@ -2725,7 +2525,7 @@
     <xf numFmtId="44" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2734,7 +2534,7 @@
     <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7854,11 +7654,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:G7">
       <formula1>"Go,Go with Risk,Redirect,TBD"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G28:G29">
+      <formula1>"open,closed"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D23">
       <formula1>"Go,Go with Risk,Redirect,TBD,Go（逾期）,Go with Risk（逾期）,Redirect（逾期）"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G28:G29">
-      <formula1>"open,closed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -7873,7 +7673,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7917,8 +7717,10 @@
       <c r="A3" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>327</v>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虚拟智能终端协同增强（TRAIN-001）</t>
+        </is>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -7930,8 +7732,10 @@
       <c r="A4" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>328</v>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR1</t>
+        </is>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -7943,8 +7747,10 @@
       <c r="A5" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>329</v>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-18</t>
+        </is>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -7956,8 +7762,10 @@
       <c r="A6" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>330</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虚拟项目经理甲</t>
+        </is>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -7969,8 +7777,10 @@
       <c r="A7" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>283</v>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -7982,8 +7792,10 @@
       <c r="A8" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>331</v>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">技术路线可行，需补齐关键器件边界、功耗预算和首轮验证计划后并行推进。</t>
+        </is>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -8025,7 +7837,7 @@
         <v>265</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="16"/>
@@ -8053,14 +7865,20 @@
       <c r="A13" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>258</v>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宋祖防</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="23"/>
@@ -8070,17 +7888,25 @@
       <c r="A14" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>333</v>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高腾飞</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">关键器件能力边界需要用样片数据闭环，否则后续方案选型存在偏差。</t>
+        </is>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="24"/>
@@ -8089,14 +7915,20 @@
       <c r="A15" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>280</v>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高大宇</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">缺席未改派</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD</t>
+        </is>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="23"/>
@@ -8106,17 +7938,25 @@
       <c r="A16" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>334</v>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">滕帅</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">链路预算对温漂和批次差异的余量不足，需要增加最差条件校核。</t>
+        </is>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="24"/>
@@ -8125,14 +7965,20 @@
       <c r="A17" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>258</v>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林世杰</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="23"/>
@@ -8140,16 +7986,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>258</v>
+        <v>329</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">罗勇平</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分参加</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="23"/>
@@ -8159,14 +8011,20 @@
       <c r="A19" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>258</v>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">梅傲寒</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">缺席未改派</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="23"/>
@@ -8176,14 +8034,20 @@
       <c r="A20" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>258</v>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吴贞奇（李俊）</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改派（正常）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="23"/>
@@ -8193,14 +8057,20 @@
       <c r="A21" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>280</v>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赵阳</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD</t>
+        </is>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="23"/>
@@ -8208,19 +8078,27 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>338</v>
+        <v>330</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杨凯</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">验证计划缺少弱网和高温组合场景，无法覆盖核心技术风险。</t>
+        </is>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="24"/>
@@ -8229,24 +8107,32 @@
       <c r="A23" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>339</v>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">刘振岩</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">质量门限应在TDR1阶段明确并与后续量产判定保持一致。</t>
+        </is>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="24"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="5" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -8322,49 +8208,77 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="32" t="s">
-        <v>341</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>343</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>344</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>345</v>
-      </c>
-      <c r="F29" s="35" t="s">
-        <v>346</v>
-      </c>
-      <c r="G29" s="36" t="s">
-        <v>347</v>
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR1-1</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高腾飞、滕帅、杨凯、刘振岩</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">关键器件边界、链路余量和组合场景验证尚未形成统一基线。</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建立统一技术基线，补充最差条件链路预算及弱网高温组合验证计划。</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评审基线文档完成会签；仿真余量不低于3 dB；组合场景用例覆盖率达到100%。</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.25：基线与验证计划已更新，等待首轮样片数据。</t>
+        </is>
+      </c>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open</t>
+        </is>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>349</v>
-      </c>
-      <c r="D30" s="34" t="s">
-        <v>350</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>351</v>
-      </c>
-      <c r="F30" s="35" t="s">
-        <v>352</v>
-      </c>
-      <c r="G30" s="36" t="s">
-        <v>320</v>
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR1-2</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林世杰</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">整机天线布局需要提前预留隔离区，避免结构冻结后返工。</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在结构草图中标记天线净空区并纳入设计检查表。</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">结构草图通过天线与结构联合评审，净空尺寸满足设计规范。</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.22：联合评审完成。</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">closed</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -8452,11 +8366,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:G7">
       <formula1>"Go,Go with Risk,Redirect,TBD"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G29:G33">
+      <formula1>"open,closed"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D24">
       <formula1>"Go,Go with Risk,Redirect,TBD,Go（逾期）,Go with Risk（逾期）,Redirect（逾期）"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G29:G33">
-      <formula1>"open,closed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -8470,7 +8384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8514,8 +8428,10 @@
       <c r="A3" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>327</v>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虚拟智能终端协同增强（TRAIN-001）</t>
+        </is>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -8527,8 +8443,10 @@
       <c r="A4" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>353</v>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR2</t>
+        </is>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -8540,8 +8458,10 @@
       <c r="A5" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>354</v>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-27</t>
+        </is>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -8553,8 +8473,10 @@
       <c r="A6" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>330</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虚拟项目经理甲</t>
+        </is>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -8566,8 +8488,10 @@
       <c r="A7" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>355</v>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Redirect</t>
+        </is>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -8579,8 +8503,10 @@
       <c r="A8" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>356</v>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">样片结果暴露高温稳定性风险，完成根因定位和回归验证前不得进入设计冻结。</t>
+        </is>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -8622,7 +8548,7 @@
         <v>265</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="16"/>
@@ -8650,14 +8576,20 @@
       <c r="A13" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>357</v>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宋祖防</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go（逾期）</t>
+        </is>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="23"/>
@@ -8667,17 +8599,25 @@
       <c r="A14" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>358</v>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高腾飞</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Redirect</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高温样片数据超过技术基线，尚不能证明方案达到冻结条件。</t>
+        </is>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="24"/>
@@ -8686,14 +8626,20 @@
       <c r="A15" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>280</v>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高大宇</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">挂会</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD</t>
+        </is>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="23"/>
@@ -8703,17 +8649,25 @@
       <c r="A16" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>360</v>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">滕帅</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分参加</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">射频校准偏差集中在高温区间，需要增加分段补偿。</t>
+        </is>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="24"/>
@@ -8722,14 +8676,20 @@
       <c r="A17" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>258</v>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林世杰</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="23"/>
@@ -8737,19 +8697,27 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>361</v>
+        <v>329</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">罗勇平</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Redirect</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">结构热路径与仿真假设不一致，需要重新核对边界条件。</t>
+        </is>
       </c>
       <c r="F18" s="23"/>
       <c r="G18" s="24"/>
@@ -8758,14 +8726,20 @@
       <c r="A19" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>280</v>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">梅傲寒</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD</t>
+        </is>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="23"/>
@@ -8775,14 +8749,20 @@
       <c r="A20" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>258</v>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吴贞奇</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="23"/>
@@ -8792,14 +8772,20 @@
       <c r="A21" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>357</v>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赵阳</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go（逾期）</t>
+        </is>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="23"/>
@@ -8807,19 +8793,27 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>363</v>
+        <v>330</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杨凯</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分参加</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Redirect</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">回归测试尚未覆盖高温连续运行和恢复场景。</t>
+        </is>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="24"/>
@@ -8828,24 +8822,32 @@
       <c r="A23" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>365</v>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">刘振岩</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk（逾期）</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">关键风险已识别，但关闭证据提交晚于会签时限。</t>
+        </is>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="24"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="5" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -8921,47 +8923,73 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>368</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>369</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>370</v>
-      </c>
-      <c r="F29" s="35" t="s">
-        <v>371</v>
-      </c>
-      <c r="G29" s="36" t="s">
-        <v>347</v>
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR2-1</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高腾飞、滕帅、刘振岩</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高温条件下链路性能下降，样片结果超出TDR1技术基线。</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完成根因分层定位，增加高温分段校准并重新执行全链路回归。</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">连续高温运行8小时无异常，链路余量不低于3 dB，三轮回归结果一致。</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06.08：校准方案已合入，第二轮回归通过。</t>
+        </is>
+      </c>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open</t>
+        </is>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>373</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>374</v>
-      </c>
-      <c r="D30" s="34" t="s">
-        <v>375</v>
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR2-2</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">罗勇平、杨凯</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">结构热路径假设与实测不一致，高温连续运行场景覆盖不足。</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">重新标定热仿真边界，并增加高温连续运行与恢复测试。</t>
+        </is>
       </c>
       <c r="E30" s="33"/>
-      <c r="F30" s="35" t="s">
-        <v>376</v>
-      </c>
-      <c r="G30" s="36" t="s">
-        <v>347</v>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06.05：边界条件已重算，测试通过条件待补充。</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -9049,11 +9077,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:G7">
       <formula1>"Go,Go with Risk,Redirect,TBD"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G29:G33">
+      <formula1>"open,closed"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D24">
       <formula1>"Go,Go with Risk,Redirect,TBD,Go（逾期）,Go with Risk（逾期）,Redirect（逾期）"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G29:G33">
-      <formula1>"open,closed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -9067,7 +9095,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9111,8 +9139,10 @@
       <c r="A3" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>327</v>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虚拟智能终端协同增强（TRAIN-001）</t>
+        </is>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -9124,8 +9154,10 @@
       <c r="A4" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>254</v>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR3</t>
+        </is>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -9137,8 +9169,10 @@
       <c r="A5" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>377</v>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-06</t>
+        </is>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -9150,8 +9184,10 @@
       <c r="A6" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>330</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虚拟项目经理甲</t>
+        </is>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -9163,8 +9199,10 @@
       <c r="A7" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>283</v>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -9176,8 +9214,10 @@
       <c r="A8" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>378</v>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">核心指标已达到目标，遗留的量产一致性和长期稳定性问题可按计划并行关闭。</t>
+        </is>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -9219,7 +9259,7 @@
         <v>265</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="16"/>
@@ -9247,14 +9287,20 @@
       <c r="A13" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>258</v>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宋祖防</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分参加</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
@@ -9264,14 +9310,20 @@
       <c r="A14" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>258</v>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高腾飞</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="23"/>
@@ -9281,14 +9333,20 @@
       <c r="A15" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>258</v>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高大宇</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分参加</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="23"/>
@@ -9298,17 +9356,25 @@
       <c r="A16" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>379</v>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">滕帅</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">量产校准参数尚未覆盖全部器件批次，需要补充抽样策略。</t>
+        </is>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="24"/>
@@ -9317,14 +9383,20 @@
       <c r="A17" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>357</v>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林世杰</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go（逾期）</t>
+        </is>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="23"/>
@@ -9332,16 +9404,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>258</v>
+        <v>329</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">罗勇平</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="23"/>
@@ -9351,14 +9429,20 @@
       <c r="A19" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>280</v>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">梅傲寒</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">挂会</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD</t>
+        </is>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="23"/>
@@ -9368,14 +9452,20 @@
       <c r="A20" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>258</v>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吴贞奇（李俊）</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改派（部分）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="23"/>
@@ -9385,36 +9475,52 @@
       <c r="A21" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>381</v>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赵阳</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">量产一致性风险需要通过三批次试产数据确认。</t>
+        </is>
       </c>
       <c r="F21" s="23"/>
       <c r="G21" s="24"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>382</v>
+        <v>330</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杨凯</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go with Risk</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长期稳定性测试已启动，但尚未达到完整周期。</t>
+        </is>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="24"/>
@@ -9423,14 +9529,20 @@
       <c r="A23" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>258</v>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">刘振岩</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">缺席未改派</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go</t>
+        </is>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="23"/>
@@ -9438,7 +9550,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="5" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -9514,47 +9626,73 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="32" t="s">
-        <v>314</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>383</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>384</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>385</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>386</v>
-      </c>
-      <c r="F29" s="35" t="s">
-        <v>387</v>
-      </c>
-      <c r="G29" s="36" t="s">
-        <v>347</v>
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR3-1</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赵阳、杨凯</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">量产一致性和长期稳定性证据尚未覆盖完整批次与周期。</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完成三批次试产抽检，并持续执行500小时稳定性测试。</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三批次关键指标通过率不低于99%；500小时测试无严重故障。</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08.10：首批试产通过，稳定性测试累计180小时。</t>
+        </is>
+      </c>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open</t>
+        </is>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>388</v>
-      </c>
-      <c r="D30" s="34" t="s">
-        <v>389</v>
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TDR3-2</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">滕帅</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">量产校准参数对器件批次差异的覆盖范围待确认。</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">补充跨批次抽样并更新校准参数边界。</t>
+        </is>
       </c>
       <c r="E30" s="33"/>
-      <c r="F30" s="35" t="s">
-        <v>390</v>
-      </c>
-      <c r="G30" s="36" t="s">
-        <v>347</v>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08.09：已完成抽样方案，判定阈值待补充。</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -9642,11 +9780,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:G7">
       <formula1>"Go,Go with Risk,Redirect,TBD"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G29:G33">
+      <formula1>"open,closed"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D24">
       <formula1>"Go,Go with Risk,Redirect,TBD,Go（逾期）,Go with Risk（逾期）,Redirect（逾期）"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G29:G33">
-      <formula1>"open,closed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/data/2026-08-11-virtual-tdrx-review-training-v0.1.xlsx
+++ b/data/2026-08-11-virtual-tdrx-review-training-v0.1.xlsx
@@ -8210,7 +8210,7 @@
     <row r="29" spans="1:7">
       <c r="A29" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TDR1-1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B29" s="32" t="inlineStr">
@@ -8247,7 +8247,7 @@
     <row r="30" spans="1:7">
       <c r="A30" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TDR1-2</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B30" s="32" t="inlineStr">
@@ -8925,7 +8925,7 @@
     <row r="29" spans="1:7">
       <c r="A29" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TDR2-1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B29" s="32" t="inlineStr">
@@ -8962,7 +8962,7 @@
     <row r="30" spans="1:7">
       <c r="A30" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TDR2-2</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B30" s="32" t="inlineStr">
@@ -9628,7 +9628,7 @@
     <row r="29" spans="1:7">
       <c r="A29" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TDR3-1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B29" s="32" t="inlineStr">
@@ -9665,7 +9665,7 @@
     <row r="30" spans="1:7">
       <c r="A30" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TDR3-2</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B30" s="32" t="inlineStr">
